--- a/outputs/tables/comparison_statistics.xlsx
+++ b/outputs/tables/comparison_statistics.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,43 +523,43 @@
         <v>0.7373409851745576</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6636585365853659</v>
+        <v>0.6645050215208035</v>
       </c>
       <c r="E2" t="n">
-        <v>0.07368244858919171</v>
+        <v>0.07283596365375411</v>
       </c>
       <c r="F2" t="n">
-        <v>58.33565974979705</v>
+        <v>57.74406205256157</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>33601</v>
+        <v>38068</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1908</v>
+        <v>1909</v>
       </c>
       <c r="K2" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="L2" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="M2" t="n">
-        <v>1.275725091491041</v>
+        <v>1.262787618431361</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7870953913716158</v>
+        <v>0.7840295119088219</v>
       </c>
       <c r="O2" t="n">
-        <v>0.9124820659971306</v>
+        <v>0.912960306073649</v>
       </c>
       <c r="P2" t="n">
-        <v>0.8541367766618843</v>
+        <v>0.8512673362027738</v>
       </c>
     </row>
     <row r="3">
@@ -572,46 +572,46 @@
         <v>2091</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7343137254901961</v>
+        <v>0.7339933046389289</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6636585365853659</v>
+        <v>0.6645050215208035</v>
       </c>
       <c r="E3" t="n">
-        <v>0.07065518890483025</v>
+        <v>0.06948828311812538</v>
       </c>
       <c r="F3" t="n">
-        <v>59.57188410184428</v>
+        <v>57.57357840818641</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>29694</v>
+        <v>34749.5</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1.992645037831852e-309</v>
       </c>
       <c r="J3" t="n">
-        <v>1902</v>
+        <v>1886</v>
       </c>
       <c r="K3" t="n">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="L3" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M3" t="n">
-        <v>1.3027597120196</v>
+        <v>1.259059362614061</v>
       </c>
       <c r="N3" t="n">
-        <v>0.793318586364941</v>
+        <v>0.7831352034997781</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9096126255380201</v>
+        <v>0.9019607843137255</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8531802965088474</v>
+        <v>0.8383548541367767</v>
       </c>
     </row>
     <row r="4">
@@ -627,43 +627,43 @@
         <v>0.7373409851745576</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7343137254901961</v>
+        <v>0.7339933046389289</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003027259684361461</v>
+        <v>0.003347680535628728</v>
       </c>
       <c r="F4" t="n">
-        <v>3.595070790532999</v>
+        <v>3.999391948069407</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0003318186982093102</v>
+        <v>6.571365990965817e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>771519</v>
+        <v>760821</v>
       </c>
       <c r="I4" t="n">
-        <v>1.121009148112077e-05</v>
+        <v>4.260592455726578e-06</v>
       </c>
       <c r="J4" t="n">
         <v>1038</v>
       </c>
       <c r="K4" t="n">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="L4" t="n">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="M4" t="n">
-        <v>0.07861952762410362</v>
+        <v>0.08746150606237253</v>
       </c>
       <c r="N4" t="n">
-        <v>0.07839630657890702</v>
+        <v>0.08714957750298809</v>
       </c>
       <c r="O4" t="n">
         <v>0.4964131994261119</v>
       </c>
       <c r="P4" t="n">
-        <v>0.09899569583931134</v>
+        <v>0.1023433763749402</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tables/comparison_statistics.xlsx
+++ b/outputs/tables/comparison_statistics.xlsx
@@ -523,43 +523,43 @@
         <v>0.7373409851745576</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6645050215208035</v>
+        <v>0.6628933524629363</v>
       </c>
       <c r="E2" t="n">
-        <v>0.07283596365375411</v>
+        <v>0.07444763271162125</v>
       </c>
       <c r="F2" t="n">
-        <v>57.74406205256157</v>
+        <v>59.34549288733826</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>38068</v>
+        <v>28180</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1909</v>
+        <v>1924</v>
       </c>
       <c r="K2" t="n">
-        <v>129</v>
+        <v>103</v>
       </c>
       <c r="L2" t="n">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="M2" t="n">
-        <v>1.262787618431361</v>
+        <v>1.297808830276303</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7840295119088219</v>
+        <v>0.7921971251581058</v>
       </c>
       <c r="O2" t="n">
-        <v>0.912960306073649</v>
+        <v>0.9201339072214252</v>
       </c>
       <c r="P2" t="n">
-        <v>0.8512673362027738</v>
+        <v>0.8708751793400287</v>
       </c>
     </row>
     <row r="3">
@@ -572,46 +572,46 @@
         <v>2091</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7339933046389289</v>
+        <v>0.7344332855093257</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6645050215208035</v>
+        <v>0.6628933524629363</v>
       </c>
       <c r="E3" t="n">
-        <v>0.06948828311812538</v>
+        <v>0.07153993304638939</v>
       </c>
       <c r="F3" t="n">
-        <v>57.57357840818641</v>
+        <v>59.40474725442622</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>34749.5</v>
+        <v>26543</v>
       </c>
       <c r="I3" t="n">
-        <v>1.992645037831852e-309</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1886</v>
+        <v>1897</v>
       </c>
       <c r="K3" t="n">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="L3" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="M3" t="n">
-        <v>1.259059362614061</v>
+        <v>1.299104646303733</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7831352034997781</v>
+        <v>0.7924914284428793</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9019607843137255</v>
+        <v>0.907221425155428</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8383548541367767</v>
+        <v>0.8522238163558106</v>
       </c>
     </row>
     <row r="4">
@@ -627,43 +627,43 @@
         <v>0.7373409851745576</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7339933046389289</v>
+        <v>0.7344332855093257</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003347680535628728</v>
+        <v>0.002907699665231855</v>
       </c>
       <c r="F4" t="n">
-        <v>3.999391948069407</v>
+        <v>3.450645445351112</v>
       </c>
       <c r="G4" t="n">
-        <v>6.571365990965817e-05</v>
+        <v>0.0005703543167067237</v>
       </c>
       <c r="H4" t="n">
-        <v>760821</v>
+        <v>771919.5</v>
       </c>
       <c r="I4" t="n">
-        <v>4.260592455726578e-06</v>
+        <v>3.252578473624868e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1038</v>
+        <v>1029</v>
       </c>
       <c r="K4" t="n">
-        <v>824</v>
+        <v>834</v>
       </c>
       <c r="L4" t="n">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="M4" t="n">
-        <v>0.08746150606237253</v>
+        <v>0.07546113295631331</v>
       </c>
       <c r="N4" t="n">
-        <v>0.08714957750298809</v>
+        <v>0.0752650915470033</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4964131994261119</v>
+        <v>0.4921090387374462</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1023433763749402</v>
+        <v>0.09325681492109039</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tables/comparison_statistics.xlsx
+++ b/outputs/tables/comparison_statistics.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -520,46 +520,46 @@
         <v>2091</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7373409851745576</v>
+        <v>0.7377905308464849</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6628933524629363</v>
+        <v>0.6647537063605931</v>
       </c>
       <c r="E2" t="n">
-        <v>0.07444763271162125</v>
+        <v>0.07303682448589188</v>
       </c>
       <c r="F2" t="n">
-        <v>59.34549288733826</v>
+        <v>59.94821371592538</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>28180</v>
+        <v>36695</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1924</v>
+        <v>1920</v>
       </c>
       <c r="K2" t="n">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="L2" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="M2" t="n">
-        <v>1.297808830276303</v>
+        <v>1.310989551767938</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7921971251581058</v>
+        <v>0.7951650789113587</v>
       </c>
       <c r="O2" t="n">
-        <v>0.9201339072214252</v>
+        <v>0.9182209469153515</v>
       </c>
       <c r="P2" t="n">
-        <v>0.8708751793400287</v>
+        <v>0.8617886178861789</v>
       </c>
     </row>
     <row r="3">
@@ -572,46 +572,46 @@
         <v>2091</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7344332855093257</v>
+        <v>0.7344237207077954</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6628933524629363</v>
+        <v>0.6647537063605931</v>
       </c>
       <c r="E3" t="n">
-        <v>0.07153993304638939</v>
+        <v>0.06967001434720232</v>
       </c>
       <c r="F3" t="n">
-        <v>59.40474725442622</v>
+        <v>59.08016657542925</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>26543</v>
+        <v>32844</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1897</v>
+        <v>1919</v>
       </c>
       <c r="K3" t="n">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="L3" t="n">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="M3" t="n">
-        <v>1.299104646303733</v>
+        <v>1.292006488535644</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7924914284428793</v>
+        <v>0.790872500086007</v>
       </c>
       <c r="O3" t="n">
-        <v>0.907221425155428</v>
+        <v>0.9177427068388331</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8522238163558106</v>
+        <v>0.8660927785748446</v>
       </c>
     </row>
     <row r="4">
@@ -624,46 +624,46 @@
         <v>2091</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7373409851745576</v>
+        <v>0.7377905308464849</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7344332855093257</v>
+        <v>0.7344237207077954</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002907699665231855</v>
+        <v>0.003366810138689558</v>
       </c>
       <c r="F4" t="n">
-        <v>3.450645445351112</v>
+        <v>3.961432788251662</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0005703543167067237</v>
+        <v>7.699886282924407e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>771919.5</v>
+        <v>755020.5</v>
       </c>
       <c r="I4" t="n">
-        <v>3.252578473624868e-05</v>
+        <v>5.222687609224084e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>1029</v>
+        <v>1040</v>
       </c>
       <c r="K4" t="n">
-        <v>834</v>
+        <v>814</v>
       </c>
       <c r="L4" t="n">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="M4" t="n">
-        <v>0.07546113295631331</v>
+        <v>0.08663138855210328</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0752650915470033</v>
+        <v>0.08632861438593628</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4921090387374462</v>
+        <v>0.4973696795791487</v>
       </c>
       <c r="P4" t="n">
-        <v>0.09325681492109039</v>
+        <v>0.1080822572931612</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tables/comparison_statistics.xlsx
+++ b/outputs/tables/comparison_statistics.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,55 +456,65 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>mean_diff_ci_low</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>mean_diff_ci_high</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>t_test_statistic</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>t_test_p</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>wilcoxon_statistic</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>wilcoxon_p</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>group1_better_count</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>group2_better_count</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>ties_count</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>cohens_d</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>r_effect_size</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>cles</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>cliffs_delta</t>
         </is>
@@ -523,43 +533,49 @@
         <v>0.7377905308464849</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6647537063605931</v>
+        <v>0.6641654710664754</v>
       </c>
       <c r="E2" t="n">
-        <v>0.07303682448589188</v>
+        <v>0.07362505978000955</v>
       </c>
       <c r="F2" t="n">
-        <v>59.94821371592538</v>
+        <v>0.07127690100430417</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.07604507412721184</v>
       </c>
       <c r="H2" t="n">
-        <v>36695</v>
+        <v>59.93641232848071</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1920</v>
+        <v>30080.5</v>
       </c>
       <c r="K2" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>53</v>
+        <v>1896</v>
       </c>
       <c r="M2" t="n">
-        <v>1.310989551767938</v>
+        <v>115</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7951650789113587</v>
+        <v>80</v>
       </c>
       <c r="O2" t="n">
-        <v>0.9182209469153515</v>
+        <v>1.310731470756389</v>
       </c>
       <c r="P2" t="n">
-        <v>0.8617886178861789</v>
+        <v>0.7951075079341539</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.9258727881396461</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.8517455762792921</v>
       </c>
     </row>
     <row r="3">
@@ -572,46 +588,52 @@
         <v>2091</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7344237207077954</v>
+        <v>0.7348158775705403</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6647537063605931</v>
+        <v>0.6641654710664754</v>
       </c>
       <c r="E3" t="n">
-        <v>0.06967001434720232</v>
+        <v>0.07065040650406496</v>
       </c>
       <c r="F3" t="n">
-        <v>59.08016657542925</v>
+        <v>0.06845994739359158</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.07300813008130082</v>
       </c>
       <c r="H3" t="n">
-        <v>32844</v>
+        <v>59.95474961370602</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1919</v>
+        <v>32389.5</v>
       </c>
       <c r="K3" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>64</v>
+        <v>1896</v>
       </c>
       <c r="M3" t="n">
-        <v>1.292006488535644</v>
+        <v>125</v>
       </c>
       <c r="N3" t="n">
-        <v>0.790872500086007</v>
+        <v>70</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9177427068388331</v>
+        <v>1.311132483361237</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8660927785748446</v>
+        <v>0.7951969538815579</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.923481587757054</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.846963175514108</v>
       </c>
     </row>
     <row r="4">
@@ -627,43 +649,49 @@
         <v>0.7377905308464849</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7344237207077954</v>
+        <v>0.7348158775705403</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003366810138689558</v>
+        <v>0.002974653275944594</v>
       </c>
       <c r="F4" t="n">
-        <v>3.961432788251662</v>
+        <v>0.001348637015781928</v>
       </c>
       <c r="G4" t="n">
-        <v>7.699886282924407e-05</v>
+        <v>0.004571975131516024</v>
       </c>
       <c r="H4" t="n">
-        <v>755020.5</v>
+        <v>3.571441718008197</v>
       </c>
       <c r="I4" t="n">
-        <v>5.222687609224084e-06</v>
+        <v>0.0003630465115809354</v>
       </c>
       <c r="J4" t="n">
-        <v>1040</v>
+        <v>771697</v>
       </c>
       <c r="K4" t="n">
-        <v>814</v>
+        <v>2.431690426512204e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>237</v>
+        <v>1073</v>
       </c>
       <c r="M4" t="n">
-        <v>0.08663138855210328</v>
+        <v>805</v>
       </c>
       <c r="N4" t="n">
-        <v>0.08632861438593628</v>
+        <v>213</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4973696795791487</v>
+        <v>0.07810279050588395</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1080822572931612</v>
+        <v>0.077884172485646</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.5640841702534672</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.1281683405069345</v>
       </c>
     </row>
   </sheetData>
